--- a/Example_Test_Recipe.xlsx
+++ b/Example_Test_Recipe.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devin\School\Senior Design\Team-108-Generation-of-Synthetic-Battery-Gas-for-Fire-and-Explosion-Testing-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08500da1c505d51b/Desktop/Senior Design/Team-108-Generation-of-Synthetic-Battery-Gas-for-Fire-and-Explosion-Testing-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14C9C86-43FD-41C9-BB7E-C9BCD4183288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7893C657-E207-4CF8-98A8-1C7CA93FFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="4245" windowWidth="28800" windowHeight="15345" xr2:uid="{2CE868BB-4CDE-422B-A877-E4D21E68C372}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2CE868BB-4CDE-422B-A877-E4D21E68C372}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,34 +36,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+  <si>
+    <t>Time (s)</t>
+  </si>
   <si>
     <t>H2</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>CO2</t>
   </si>
   <si>
+    <t>C2H4</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
     <t>N2</t>
   </si>
   <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>O2</t>
-  </si>
-  <si>
     <t>Heat Release Rate (kW)</t>
   </si>
   <si>
-    <t>Time (s)</t>
+    <t>H2 SLPM</t>
+  </si>
+  <si>
+    <t>CO SLPM</t>
+  </si>
+  <si>
+    <t>CO2 SLPM</t>
+  </si>
+  <si>
+    <t>C2H4 SLPM</t>
+  </si>
+  <si>
+    <t>CH4 SLPM</t>
+  </si>
+  <si>
+    <t>N2 SLPM</t>
+  </si>
+  <si>
+    <t>Heat of Combustion (kJ/kg)</t>
+  </si>
+  <si>
+    <t>Fuel Density at STP (g/L)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,16 +98,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -88,15 +139,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -109,6 +205,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,381 +528,775 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1205A373-0027-4370-B8D0-F88183E8D924}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" customWidth="1"/>
+    <col min="11" max="12" width="13.81640625" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+    </row>
+    <row r="3" spans="1:14" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1">
+        <v>141584</v>
+      </c>
+      <c r="C3" s="1">
+        <v>10104</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>50285</v>
+      </c>
+      <c r="F3" s="1">
+        <v>55514</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1.145</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.96</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.71679999999999999</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.1779999999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.2490000000000001</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>100</v>
+      </c>
+      <c r="I5" s="3">
+        <f>(B5*(H5/$B$3)*60000)/$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <f>(C5*(H5/$C$3)*60000)/$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
+        <f>(E5*(H5/$E$3)*60000)/$E$4</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <f>(F5*(H5/$F$3)*60000)/$F$4</f>
+        <v>91.749443524333458</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" ref="I6:I18" si="0">(B6*(H6/$B$3)*60000)/$B$4</f>
+        <v>28.28320564618263</v>
+      </c>
+      <c r="J6" s="3">
+        <f t="shared" ref="J6:J18" si="1">(C6*(H6/$C$3)*60000)/$C$4</f>
+        <v>31.117426796253465</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3">
+        <f t="shared" ref="L6:L18" si="2">(E6*(H6/$E$3)*60000)/$E$4</f>
+        <v>4.9938564468245286</v>
+      </c>
+      <c r="M6" s="3">
+        <f t="shared" ref="M6:M17" si="3">(F6*(H6/$F$3)*60000)/$F$4</f>
+        <v>5.5049666114600075</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="B7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>50</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>70.708014115456578</v>
+      </c>
+      <c r="J7" s="3">
+        <f t="shared" si="1"/>
+        <v>25.931188996877882</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3230940780408815</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="3"/>
+        <v>9.1749443524333465</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B8" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>50</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>58.923345096213815</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="1"/>
+        <v>25.931188996877882</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3230940780408815</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="3"/>
+        <v>9.1749443524333465</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>50</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>47.138676076971052</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" si="1"/>
+        <v>25.931188996877882</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3230940780408815</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="3"/>
+        <v>9.1749443524333465</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>0.1</v>
-      </c>
-      <c r="C3">
-        <v>0.3</v>
-      </c>
-      <c r="D3">
-        <v>0.3</v>
-      </c>
-      <c r="E3">
-        <v>0.1</v>
-      </c>
-      <c r="F3">
-        <v>0.2</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>0.2</v>
-      </c>
-      <c r="C4">
-        <v>0.2</v>
-      </c>
-      <c r="D4">
-        <v>0.3</v>
-      </c>
-      <c r="E4">
-        <v>0.1</v>
-      </c>
-      <c r="F4">
-        <v>0.2</v>
-      </c>
-      <c r="G4">
+      <c r="B10" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>0.3</v>
-      </c>
-      <c r="C5">
-        <v>0.1</v>
-      </c>
-      <c r="D5">
-        <v>0.3</v>
-      </c>
-      <c r="E5">
-        <v>0.1</v>
-      </c>
-      <c r="F5">
-        <v>0.2</v>
-      </c>
-      <c r="G5">
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>35.354007057728289</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="1"/>
+        <v>25.931188996877882</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3230940780408815</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="3"/>
+        <v>9.1749443524333465</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>0.25</v>
-      </c>
-      <c r="C6">
-        <v>0.1</v>
-      </c>
-      <c r="D6">
-        <v>0.35</v>
-      </c>
-      <c r="E6">
-        <v>0.1</v>
-      </c>
-      <c r="F6">
-        <v>0.2</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0.2</v>
-      </c>
-      <c r="C7">
-        <v>0.1</v>
-      </c>
-      <c r="D7">
-        <v>0.4</v>
-      </c>
-      <c r="E7">
-        <v>0.1</v>
-      </c>
-      <c r="F7">
-        <v>0.2</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0.15</v>
-      </c>
-      <c r="C8">
-        <v>0.1</v>
-      </c>
-      <c r="D8">
-        <v>0.45</v>
-      </c>
-      <c r="E8">
-        <v>0.1</v>
-      </c>
-      <c r="F8">
-        <v>0.2</v>
-      </c>
-      <c r="G8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>23.569338038485526</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="1"/>
+        <v>25.931188996877882</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3">
+        <f t="shared" si="2"/>
+        <v>8.3230940780408815</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="3"/>
+        <v>9.1749443524333465</v>
+      </c>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>0.1</v>
-      </c>
-      <c r="C9">
-        <v>0.1</v>
-      </c>
-      <c r="D9">
+      <c r="B12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="3">
         <v>0.5</v>
       </c>
-      <c r="E9">
-        <v>0.1</v>
-      </c>
-      <c r="F9">
-        <v>0.2</v>
-      </c>
-      <c r="G9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="E12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>75</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>35.354007057728289</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="1"/>
+        <v>38.896783495316825</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
+        <f t="shared" si="2"/>
+        <v>12.484641117061324</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="3"/>
+        <v>13.762416528650016</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>0.1</v>
-      </c>
-      <c r="C10">
-        <v>0.1</v>
-      </c>
-      <c r="D10">
+      <c r="B13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>75</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>35.354007057728289</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="1"/>
+        <v>38.896783495316825</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="3"/>
+        <v>13.762416528650016</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>75</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <f t="shared" si="1"/>
+        <v>38.896783495316825</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3">
+        <f t="shared" si="2"/>
+        <v>12.484641117061324</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" si="3"/>
+        <v>13.762416528650016</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>75</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <f t="shared" si="1"/>
+        <v>38.896783495316825</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <f t="shared" si="2"/>
+        <v>12.484641117061324</v>
+      </c>
+      <c r="M15" s="3">
+        <f t="shared" si="3"/>
+        <v>13.762416528650016</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3">
         <v>0.5</v>
       </c>
-      <c r="E10">
-        <v>0.1</v>
-      </c>
-      <c r="F10">
-        <v>0.2</v>
-      </c>
-      <c r="G10">
+      <c r="C16" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0.1</v>
-      </c>
-      <c r="C11">
-        <v>0.1</v>
-      </c>
-      <c r="D11">
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>176.77003528864142</v>
+      </c>
+      <c r="J16" s="3">
+        <f t="shared" si="1"/>
+        <v>38.896783495316825</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <f t="shared" si="2"/>
+        <v>12.484641117061324</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="3"/>
+        <v>13.762416528650016</v>
+      </c>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="3">
         <v>0.6</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0.2</v>
-      </c>
-      <c r="G11">
+      <c r="E17" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0.1</v>
-      </c>
-      <c r="D12">
-        <v>0.6</v>
-      </c>
-      <c r="E12">
-        <v>0.1</v>
-      </c>
-      <c r="F12">
-        <v>0.2</v>
-      </c>
-      <c r="G12">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0.1</v>
-      </c>
-      <c r="D13">
-        <v>0.6</v>
-      </c>
-      <c r="E13">
-        <v>0.1</v>
-      </c>
-      <c r="F13">
-        <v>0.2</v>
-      </c>
-      <c r="G13">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>0.5</v>
-      </c>
-      <c r="C14">
-        <v>0.1</v>
-      </c>
-      <c r="D14">
-        <v>0.1</v>
-      </c>
-      <c r="E14">
-        <v>0.1</v>
-      </c>
-      <c r="F14">
-        <v>0.2</v>
-      </c>
-      <c r="G14">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <f t="shared" si="1"/>
+        <v>38.896783495316825</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3">
+        <f t="shared" si="2"/>
+        <v>12.484641117061324</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="3"/>
+        <v>13.762416528650016</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0.1</v>
-      </c>
-      <c r="D15">
-        <v>0.6</v>
-      </c>
-      <c r="E15">
-        <v>0.1</v>
-      </c>
-      <c r="F15">
-        <v>0.2</v>
-      </c>
-      <c r="G15">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
+      <c r="B18" s="3">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" ref="M18" si="4">(F18*(H18/$F$3)*60000)/$F$4</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="N1:N4"/>
+    <mergeCell ref="H1:H4"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="J1:J4"/>
+    <mergeCell ref="K1:K4"/>
+    <mergeCell ref="L1:L4"/>
+    <mergeCell ref="M1:M4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Example_Test_Recipe.xlsx
+++ b/Example_Test_Recipe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08500da1c505d51b/Desktop/Senior Design/Team-108-Generation-of-Synthetic-Battery-Gas-for-Fire-and-Explosion-Testing-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Devin\School\Senior Design\Team-108-Generation-of-Synthetic-Battery-Gas-for-Fire-and-Explosion-Testing-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7893C657-E207-4CF8-98A8-1C7CA93FFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE28EC0-B5B1-480D-B816-87485B017A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2CE868BB-4CDE-422B-A877-E4D21E68C372}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2CE868BB-4CDE-422B-A877-E4D21E68C372}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>Time (s)</t>
   </si>
@@ -56,9 +56,6 @@
     <t>CH4</t>
   </si>
   <si>
-    <t>N2</t>
-  </si>
-  <si>
     <t>Heat Release Rate (kW)</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
   </si>
   <si>
     <t>CH4 SLPM</t>
-  </si>
-  <si>
-    <t>N2 SLPM</t>
   </si>
   <si>
     <t>Heat of Combustion (kJ/kg)</t>
@@ -103,6 +97,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -110,6 +105,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -131,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -169,23 +165,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -205,10 +250,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -528,18 +569,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1205A373-0027-4370-B8D0-F88183E8D924}">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" customWidth="1"/>
-    <col min="8" max="8" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" customWidth="1"/>
-    <col min="11" max="12" width="13.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="11" width="13.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,13 +599,13 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -576,14 +617,8 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -600,20 +635,16 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="5"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:14" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
         <v>141584</v>
@@ -630,20 +661,16 @@
       <c r="F3" s="1">
         <v>55514</v>
       </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="5"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
         <v>8.9899999999999994E-2</v>
@@ -660,18 +687,14 @@
       <c r="F4" s="1">
         <v>1.1779999999999999</v>
       </c>
-      <c r="G4" s="1">
-        <v>1.2490000000000001</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0</v>
       </c>
@@ -691,31 +714,27 @@
         <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="3">
-        <v>100</v>
+        <f>(B5*(G5/$B$3)*60000)/$B$4</f>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <f>(B5*(H5/$B$3)*60000)/$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <f>(C5*(H5/$C$3)*60000)/$C$4</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="3"/>
+        <f>(C5*(G5/$C$3)*60000)/$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3">
+        <f>(E5*(G5/$E$3)*60000)/$E$4</f>
+        <v>0</v>
+      </c>
       <c r="L5" s="3">
-        <f>(E5*(H5/$E$3)*60000)/$E$4</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <f>(F5*(H5/$F$3)*60000)/$F$4</f>
+        <f>(F5*(G5/$F$3)*60000)/$F$4</f>
         <v>91.749443524333458</v>
       </c>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -735,31 +754,27 @@
         <v>0.2</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H6" s="3">
-        <v>30</v>
+        <f>(B6*(G6/$B$3)*60000)/$B$4</f>
+        <v>28.28320564618263</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" ref="I6:I18" si="0">(B6*(H6/$B$3)*60000)/$B$4</f>
-        <v>28.28320564618263</v>
-      </c>
-      <c r="J6" s="3">
-        <f t="shared" ref="J6:J18" si="1">(C6*(H6/$C$3)*60000)/$C$4</f>
+        <f>(C6*(G6/$C$3)*60000)/$C$4</f>
         <v>31.117426796253465</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3">
+        <f>(E6*(G6/$E$3)*60000)/$E$4</f>
+        <v>4.9938564468245286</v>
+      </c>
       <c r="L6" s="3">
-        <f t="shared" ref="L6:L18" si="2">(E6*(H6/$E$3)*60000)/$E$4</f>
-        <v>4.9938564468245286</v>
-      </c>
-      <c r="M6" s="3">
-        <f t="shared" ref="M6:M17" si="3">(F6*(H6/$F$3)*60000)/$F$4</f>
+        <f>(F6*(G6/$F$3)*60000)/$F$4</f>
         <v>5.5049666114600075</v>
       </c>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -779,31 +794,27 @@
         <v>0.2</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H7" s="3">
-        <v>50</v>
+        <f>(B7*(G7/$B$3)*60000)/$B$4</f>
+        <v>70.708014115456578</v>
       </c>
       <c r="I7" s="3">
-        <f t="shared" si="0"/>
-        <v>70.708014115456578</v>
-      </c>
-      <c r="J7" s="3">
-        <f t="shared" si="1"/>
+        <f>(C7*(G7/$C$3)*60000)/$C$4</f>
         <v>25.931188996877882</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3">
+        <f>(E7*(G7/$E$3)*60000)/$E$4</f>
+        <v>8.3230940780408815</v>
+      </c>
       <c r="L7" s="3">
-        <f t="shared" si="2"/>
-        <v>8.3230940780408815</v>
-      </c>
-      <c r="M7" s="3">
-        <f t="shared" si="3"/>
+        <f>(F7*(G7/$F$3)*60000)/$F$4</f>
         <v>9.1749443524333465</v>
       </c>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -823,31 +834,27 @@
         <v>0.2</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3">
-        <v>50</v>
+        <f>(B8*(G8/$B$3)*60000)/$B$4</f>
+        <v>58.923345096213815</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="0"/>
-        <v>58.923345096213815</v>
-      </c>
-      <c r="J8" s="3">
-        <f t="shared" si="1"/>
+        <f>(C8*(G8/$C$3)*60000)/$C$4</f>
         <v>25.931188996877882</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3">
+        <f>(E8*(G8/$E$3)*60000)/$E$4</f>
+        <v>8.3230940780408815</v>
+      </c>
       <c r="L8" s="3">
-        <f t="shared" si="2"/>
-        <v>8.3230940780408815</v>
-      </c>
-      <c r="M8" s="3">
-        <f t="shared" si="3"/>
+        <f>(F8*(G8/$F$3)*60000)/$F$4</f>
         <v>9.1749443524333465</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -867,31 +874,27 @@
         <v>0.2</v>
       </c>
       <c r="G9" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3">
-        <v>50</v>
+        <f>(B9*(G9/$B$3)*60000)/$B$4</f>
+        <v>47.138676076971052</v>
       </c>
       <c r="I9" s="3">
-        <f t="shared" si="0"/>
-        <v>47.138676076971052</v>
-      </c>
-      <c r="J9" s="3">
-        <f t="shared" si="1"/>
+        <f>(C9*(G9/$C$3)*60000)/$C$4</f>
         <v>25.931188996877882</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3">
+        <f>(E9*(G9/$E$3)*60000)/$E$4</f>
+        <v>8.3230940780408815</v>
+      </c>
       <c r="L9" s="3">
-        <f t="shared" si="2"/>
-        <v>8.3230940780408815</v>
-      </c>
-      <c r="M9" s="3">
-        <f t="shared" si="3"/>
+        <f>(F9*(G9/$F$3)*60000)/$F$4</f>
         <v>9.1749443524333465</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -911,31 +914,27 @@
         <v>0.2</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H10" s="3">
-        <v>50</v>
+        <f>(B10*(G10/$B$3)*60000)/$B$4</f>
+        <v>35.354007057728289</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="0"/>
-        <v>35.354007057728289</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="1"/>
+        <f>(C10*(G10/$C$3)*60000)/$C$4</f>
         <v>25.931188996877882</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3">
+        <f>(E10*(G10/$E$3)*60000)/$E$4</f>
+        <v>8.3230940780408815</v>
+      </c>
       <c r="L10" s="3">
-        <f t="shared" si="2"/>
-        <v>8.3230940780408815</v>
-      </c>
-      <c r="M10" s="3">
-        <f t="shared" si="3"/>
+        <f>(F10*(G10/$F$3)*60000)/$F$4</f>
         <v>9.1749443524333465</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -955,31 +954,27 @@
         <v>0.2</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3">
-        <v>50</v>
+        <f>(B11*(G11/$B$3)*60000)/$B$4</f>
+        <v>23.569338038485526</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="0"/>
-        <v>23.569338038485526</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="1"/>
+        <f>(C11*(G11/$C$3)*60000)/$C$4</f>
         <v>25.931188996877882</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3">
+        <f>(E11*(G11/$E$3)*60000)/$E$4</f>
+        <v>8.3230940780408815</v>
+      </c>
       <c r="L11" s="3">
-        <f t="shared" si="2"/>
-        <v>8.3230940780408815</v>
-      </c>
-      <c r="M11" s="3">
-        <f t="shared" si="3"/>
+        <f>(F11*(G11/$F$3)*60000)/$F$4</f>
         <v>9.1749443524333465</v>
       </c>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -999,31 +994,27 @@
         <v>0.2</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H12" s="3">
-        <v>75</v>
+        <f>(B12*(G12/$B$3)*60000)/$B$4</f>
+        <v>35.354007057728289</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="0"/>
-        <v>35.354007057728289</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="1"/>
+        <f>(C12*(G12/$C$3)*60000)/$C$4</f>
         <v>38.896783495316825</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3">
+        <f>(E12*(G12/$E$3)*60000)/$E$4</f>
+        <v>12.484641117061324</v>
+      </c>
       <c r="L12" s="3">
-        <f t="shared" si="2"/>
-        <v>12.484641117061324</v>
-      </c>
-      <c r="M12" s="3">
-        <f t="shared" si="3"/>
+        <f>(F12*(G12/$F$3)*60000)/$F$4</f>
         <v>13.762416528650016</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -1043,31 +1034,27 @@
         <v>0.2</v>
       </c>
       <c r="G13" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H13" s="3">
-        <v>75</v>
+        <f>(B13*(G13/$B$3)*60000)/$B$4</f>
+        <v>35.354007057728289</v>
       </c>
       <c r="I13" s="3">
-        <f t="shared" si="0"/>
-        <v>35.354007057728289</v>
-      </c>
-      <c r="J13" s="3">
-        <f t="shared" si="1"/>
+        <f>(C13*(G13/$C$3)*60000)/$C$4</f>
         <v>38.896783495316825</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3">
+        <f>(E13*(G13/$E$3)*60000)/$E$4</f>
+        <v>0</v>
+      </c>
       <c r="L13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <f t="shared" si="3"/>
+        <f>(F13*(G13/$F$3)*60000)/$F$4</f>
         <v>13.762416528650016</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -1087,31 +1074,27 @@
         <v>0.2</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H14" s="3">
-        <v>75</v>
+        <f>(B14*(G14/$B$3)*60000)/$B$4</f>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <f t="shared" si="1"/>
+        <f>(C14*(G14/$C$3)*60000)/$C$4</f>
         <v>38.896783495316825</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3">
+        <f>(E14*(G14/$E$3)*60000)/$E$4</f>
+        <v>12.484641117061324</v>
+      </c>
       <c r="L14" s="3">
-        <f t="shared" si="2"/>
-        <v>12.484641117061324</v>
-      </c>
-      <c r="M14" s="3">
-        <f t="shared" si="3"/>
+        <f>(F14*(G14/$F$3)*60000)/$F$4</f>
         <v>13.762416528650016</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>10</v>
       </c>
@@ -1131,31 +1114,27 @@
         <v>0.2</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H15" s="3">
-        <v>75</v>
+        <f>(B15*(G15/$B$3)*60000)/$B$4</f>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <f t="shared" si="1"/>
+        <f>(C15*(G15/$C$3)*60000)/$C$4</f>
         <v>38.896783495316825</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3">
+        <f>(E15*(G15/$E$3)*60000)/$E$4</f>
+        <v>12.484641117061324</v>
+      </c>
       <c r="L15" s="3">
-        <f t="shared" si="2"/>
-        <v>12.484641117061324</v>
-      </c>
-      <c r="M15" s="3">
-        <f t="shared" si="3"/>
+        <f>(F15*(G15/$F$3)*60000)/$F$4</f>
         <v>13.762416528650016</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>11</v>
       </c>
@@ -1175,31 +1154,27 @@
         <v>0.2</v>
       </c>
       <c r="G16" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H16" s="3">
-        <v>75</v>
+        <f>(B16*(G16/$B$3)*60000)/$B$4</f>
+        <v>176.77003528864142</v>
       </c>
       <c r="I16" s="3">
-        <f t="shared" si="0"/>
-        <v>176.77003528864142</v>
-      </c>
-      <c r="J16" s="3">
-        <f t="shared" si="1"/>
+        <f>(C16*(G16/$C$3)*60000)/$C$4</f>
         <v>38.896783495316825</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3">
+        <f>(E16*(G16/$E$3)*60000)/$E$4</f>
+        <v>12.484641117061324</v>
+      </c>
       <c r="L16" s="3">
-        <f t="shared" si="2"/>
-        <v>12.484641117061324</v>
-      </c>
-      <c r="M16" s="3">
-        <f t="shared" si="3"/>
+        <f>(F16*(G16/$F$3)*60000)/$F$4</f>
         <v>13.762416528650016</v>
       </c>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>13</v>
       </c>
@@ -1219,31 +1194,27 @@
         <v>0.2</v>
       </c>
       <c r="G17" s="3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H17" s="3">
-        <v>75</v>
+        <f>(B17*(G17/$B$3)*60000)/$B$4</f>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <f t="shared" si="1"/>
+        <f>(C17*(G17/$C$3)*60000)/$C$4</f>
         <v>38.896783495316825</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3">
+        <f>(E17*(G17/$E$3)*60000)/$E$4</f>
+        <v>12.484641117061324</v>
+      </c>
       <c r="L17" s="3">
-        <f t="shared" si="2"/>
-        <v>12.484641117061324</v>
-      </c>
-      <c r="M17" s="3">
-        <f t="shared" si="3"/>
+        <f>(F17*(G17/$F$3)*60000)/$F$4</f>
         <v>13.762416528650016</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -1266,36 +1237,31 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
+        <f>(B18*(G18/$B$3)*60000)/$B$4</f>
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="3"/>
+        <f>(C18*(G18/$C$3)*60000)/$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3">
+        <f>(E18*(G18/$E$3)*60000)/$E$4</f>
+        <v>0</v>
+      </c>
       <c r="L18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <f t="shared" ref="M18" si="4">(F18*(H18/$F$3)*60000)/$F$4</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="3"/>
+        <f>(F18*(G18/$F$3)*60000)/$F$4</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="N1:N4"/>
+  <mergeCells count="6">
+    <mergeCell ref="G1:G4"/>
     <mergeCell ref="H1:H4"/>
     <mergeCell ref="I1:I4"/>
     <mergeCell ref="J1:J4"/>
     <mergeCell ref="K1:K4"/>
     <mergeCell ref="L1:L4"/>
-    <mergeCell ref="M1:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
